--- a/resources/Programmes/programmematernellemoyennesection.xlsx
+++ b/resources/Programmes/programmematernellemoyennesection.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JEANNE\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7155"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Feuille 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
   <si>
     <t>Activité</t>
   </si>
@@ -176,31 +184,47 @@
   </si>
   <si>
     <t>Introduction au concept de nombres, comptage, reconnaissance des chiffres</t>
+  </si>
+  <si>
+    <t>Mode_evaluation</t>
+  </si>
+  <si>
+    <t>bareme</t>
+  </si>
+  <si>
+    <t>type_exercices</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>leçons</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -210,45 +234,69 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -438,386 +486,566 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" customWidth="1"/>
+    <col min="9" max="10" width="16.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="H2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="H3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="H4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="H5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="H6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="H7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="H8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="H9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="G10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="H10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="H11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="G12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="H12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="G13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="H13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="G14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="H14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="G15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
+      <c r="H15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/resources/Programmes/programmematernellemoyennesection.xlsx
+++ b/resources/Programmes/programmematernellemoyennesection.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JEANNE\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\gestionscolaire\resources\Programmes\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7155"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8445"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="62">
   <si>
     <t>Activité</t>
   </si>
@@ -186,19 +186,25 @@
     <t>Introduction au concept de nombres, comptage, reconnaissance des chiffres</t>
   </si>
   <si>
-    <t>Mode_evaluation</t>
-  </si>
-  <si>
     <t>bareme</t>
   </si>
   <si>
     <t>type_exercices</t>
   </si>
   <si>
-    <t>null</t>
-  </si>
-  <si>
     <t>leçons</t>
+  </si>
+  <si>
+    <t>mode_evaluation</t>
+  </si>
+  <si>
+    <t>heure_debut</t>
+  </si>
+  <si>
+    <t>heure_fin</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
 </sst>
 </file>
@@ -264,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -277,7 +283,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,7 +501,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -504,11 +509,15 @@
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.140625" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" customWidth="1"/>
-    <col min="9" max="10" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" customWidth="1"/>
+    <col min="10" max="10" width="21.28515625" customWidth="1"/>
+    <col min="11" max="12" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -519,10 +528,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -531,13 +540,19 @@
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -548,10 +563,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>8</v>
@@ -560,13 +575,19 @@
         <v>9</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -577,10 +598,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -589,13 +610,19 @@
         <v>14</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -606,10 +633,10 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>8</v>
@@ -618,13 +645,19 @@
         <v>18</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -635,10 +668,10 @@
         <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>8</v>
@@ -647,13 +680,19 @@
         <v>9</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
@@ -664,10 +703,10 @@
         <v>24</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>8</v>
@@ -675,14 +714,20 @@
       <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -693,10 +738,10 @@
         <v>28</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>29</v>
@@ -704,14 +749,20 @@
       <c r="G7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -722,10 +773,10 @@
         <v>32</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>33</v>
@@ -733,14 +784,20 @@
       <c r="G8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>34</v>
       </c>
@@ -751,10 +808,10 @@
         <v>36</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>8</v>
@@ -762,14 +819,20 @@
       <c r="G9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
@@ -780,10 +843,10 @@
         <v>39</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>8</v>
@@ -791,14 +854,18 @@
       <c r="G10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="H10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -814,8 +881,10 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+    </row>
+    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -826,10 +895,10 @@
         <v>42</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>33</v>
@@ -837,14 +906,18 @@
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+      <c r="H11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -860,8 +933,10 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+    </row>
+    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
@@ -872,10 +947,10 @@
         <v>45</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>8</v>
@@ -883,14 +958,18 @@
       <c r="G12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="H12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -906,8 +985,10 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+    </row>
+    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>46</v>
       </c>
@@ -918,10 +999,10 @@
         <v>48</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>33</v>
@@ -929,14 +1010,18 @@
       <c r="G13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="H13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -952,8 +1037,10 @@
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+    </row>
+    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>49</v>
       </c>
@@ -964,10 +1051,10 @@
         <v>51</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>29</v>
@@ -975,14 +1062,18 @@
       <c r="G14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="H14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -998,8 +1089,10 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+    </row>
+    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>52</v>
       </c>
@@ -1010,10 +1103,10 @@
         <v>54</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>33</v>
@@ -1021,14 +1114,18 @@
       <c r="G15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="H15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1044,6 +1141,8 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
